--- a/diverse/tidsplan-V26.xlsx
+++ b/diverse/tidsplan-V26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\met4\diverse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64D3536-3FBE-49AC-A64A-600BF5EA7A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54678B43-55E1-4598-B7B7-4E70EF27C0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{904F4144-1937-4711-AEEF-991D1AD6F23A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{904F4144-1937-4711-AEEF-991D1AD6F23A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -149,9 +149,6 @@
     <t>04.03.: **Regnegrupper**  i Aud A.</t>
   </si>
   <si>
-    <t>11.03.: **Oppgaveseminar 5** Aud A. Se \@ref(seminar) for oppgaver.</t>
-  </si>
-  <si>
     <t>09.03.:  **Oversiktsforelesning: Tidsrekker** i Aud A</t>
   </si>
   <si>
@@ -170,10 +167,13 @@
     <t>13.04.:   **Kontakttime** i Aud A</t>
   </si>
   <si>
-    <t>16.03.: (Ingen aktivitet)</t>
-  </si>
-  <si>
     <t>15.04.: **Kontakttime**  i Aud A.</t>
+  </si>
+  <si>
+    <t>16.03.: **Oppgaveseminar 5** Aud A. Se \@ref(seminar) for oppgaver.</t>
+  </si>
+  <si>
+    <t>11.03.: (Ingen aktivitet)</t>
   </si>
 </sst>
 </file>
@@ -526,15 +526,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D0459C-A0F7-4603-AE4B-86A7155DF567}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="65.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="65.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -548,7 +548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2</v>
       </c>
@@ -562,7 +562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3</v>
       </c>
@@ -576,7 +576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>4</v>
       </c>
@@ -590,7 +590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>5</v>
       </c>
@@ -604,7 +604,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>6</v>
       </c>
@@ -618,7 +618,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>7</v>
       </c>
@@ -632,7 +632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>8</v>
       </c>
@@ -646,7 +646,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>9</v>
       </c>
@@ -660,7 +660,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>10</v>
       </c>
@@ -674,7 +674,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>11</v>
       </c>
@@ -682,13 +682,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>12</v>
       </c>
@@ -699,10 +699,10 @@
         <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>13</v>
       </c>
@@ -710,13 +710,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
         <v>41</v>
       </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>14</v>
       </c>
@@ -730,7 +730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>15</v>
       </c>
@@ -741,10 +741,10 @@
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>16</v>
       </c>
@@ -752,10 +752,10 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
         <v>44</v>
-      </c>
-      <c r="D16" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
